--- a/artfynd/A 49032-2024 artfynd.xlsx
+++ b/artfynd/A 49032-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107739968</v>
+        <v>136542287</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>43280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>101248</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Styggberget, Byom, Nyhem, Jmt</t>
+          <t>Z727 Nyhem, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536947</v>
+        <v>537094</v>
       </c>
       <c r="R2" t="n">
-        <v>6985623</v>
+        <v>6985666</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,16 +765,134 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136542287</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107739968</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Styggberget, Byom, Nyhem, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536947</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6985623</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Daniel Hedenbo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Daniel Hedenbo</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107739968</t>
         </is>
@@ -795,6 +901,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49032-2024 artfynd.xlsx
+++ b/artfynd/A 49032-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542287</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49032-2024 artfynd.xlsx
+++ b/artfynd/A 49032-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542287</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49032-2024 artfynd.xlsx
+++ b/artfynd/A 49032-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542287</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
